--- a/admin/editions/default/core_conf.xlsx
+++ b/admin/editions/default/core_conf.xlsx
@@ -227,11 +227,12 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -250,12 +251,6 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -304,7 +299,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -317,24 +312,16 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -579,7 +566,7 @@
       </c>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
         <v>4</v>
       </c>
@@ -591,7 +578,7 @@
       </c>
       <c r="D10" s="4"/>
     </row>
-    <row r="11" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
         <v>4</v>
       </c>
@@ -603,7 +590,7 @@
       </c>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
         <v>4</v>
       </c>
@@ -675,7 +662,7 @@
       </c>
       <c r="D17" s="4"/>
     </row>
-    <row r="18" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -687,7 +674,7 @@
       </c>
       <c r="D18" s="4"/>
     </row>
-    <row r="19" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
         <v>20</v>
       </c>
@@ -747,7 +734,7 @@
       </c>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
         <v>20</v>
       </c>
@@ -759,7 +746,7 @@
       </c>
       <c r="D24" s="4"/>
     </row>
-    <row r="25" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
         <v>20</v>
       </c>
@@ -819,7 +806,7 @@
       </c>
       <c r="D29" s="4"/>
     </row>
-    <row r="30" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
         <v>20</v>
       </c>
@@ -831,7 +818,7 @@
       </c>
       <c r="D30" s="4"/>
     </row>
-    <row r="31" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
         <v>20</v>
       </c>
@@ -855,7 +842,7 @@
       </c>
       <c r="D32" s="4"/>
     </row>
-    <row r="33" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
         <v>27</v>
       </c>
@@ -874,7 +861,7 @@
       <c r="B34" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D34" s="4"/>
@@ -975,7 +962,7 @@
       </c>
       <c r="D42" s="4"/>
     </row>
-    <row r="43" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
         <v>27</v>
       </c>
@@ -994,7 +981,7 @@
       <c r="B44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D44" s="4"/>
@@ -1095,49 +1082,49 @@
       </c>
       <c r="D52" s="4"/>
     </row>
-    <row r="53" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="6" t="s">
+    <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="5" t="s">
         <v>40</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="C53" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="6" t="s">
+    <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="5" t="s">
         <v>40</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C54" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="6" t="s">
+    <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="5" t="s">
         <v>40</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="C55" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
         <v>40</v>
       </c>
@@ -1149,7 +1136,7 @@
       </c>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
         <v>40</v>
       </c>
@@ -1161,189 +1148,189 @@
       </c>
       <c r="D57" s="4"/>
     </row>
-    <row r="58" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C58" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D58" s="4"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="5" t="s">
+      <c r="A59" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B59" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C59" s="5" t="s">
+      <c r="B59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D59" s="5" t="s">
+      <c r="D59" s="3" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="5" t="s">
+      <c r="A60" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B60" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C60" s="5" t="s">
+      <c r="B60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D60" s="5" t="s">
+      <c r="D60" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="5" t="s">
+    <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B61" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C61" s="5" t="s">
+      <c r="B61" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D61" s="7"/>
-    </row>
-    <row r="62" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="5" t="s">
+      <c r="D61" s="4"/>
+    </row>
+    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B62" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C62" s="5" t="s">
+      <c r="B62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="7"/>
-    </row>
-    <row r="63" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="5" t="s">
+      <c r="D62" s="4"/>
+    </row>
+    <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B63" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C63" s="5" t="s">
+      <c r="B63" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D63" s="7"/>
+      <c r="D63" s="4"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="5" t="s">
+      <c r="A64" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B64" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C64" s="5" t="s">
+      <c r="B64" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D64" s="7"/>
-    </row>
-    <row r="65" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="5" t="s">
+      <c r="D64" s="4"/>
+    </row>
+    <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B65" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C65" s="5" t="s">
+      <c r="B65" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D65" s="7"/>
-    </row>
-    <row r="66" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="5" t="s">
+      <c r="D65" s="4"/>
+    </row>
+    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B66" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C66" s="5" t="s">
+      <c r="B66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D66" s="7"/>
-    </row>
-    <row r="67" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="5" t="s">
+      <c r="D66" s="4"/>
+    </row>
+    <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B67" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C67" s="5" t="s">
+      <c r="B67" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D67" s="7"/>
-    </row>
-    <row r="68" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="5" t="s">
+      <c r="D67" s="4"/>
+    </row>
+    <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B68" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C68" s="5" t="s">
+      <c r="B68" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D68" s="7"/>
-    </row>
-    <row r="69" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="5" t="s">
+      <c r="D68" s="4"/>
+    </row>
+    <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B69" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C69" s="5" t="s">
+      <c r="B69" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D69" s="7"/>
-    </row>
-    <row r="70" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="5" t="s">
+      <c r="D69" s="4"/>
+    </row>
+    <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B70" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C70" s="5" t="s">
+      <c r="B70" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C70" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D70" s="7"/>
-    </row>
-    <row r="71" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="5" t="s">
+      <c r="D70" s="4"/>
+    </row>
+    <row r="71" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B71" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C71" s="5" t="s">
+      <c r="B71" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D71" s="7"/>
-    </row>
-    <row r="72" customFormat="false" ht="24.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="5" t="s">
+      <c r="D71" s="4"/>
+    </row>
+    <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B72" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C72" s="5" t="s">
+      <c r="B72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D72" s="7"/>
+      <c r="D72" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
